--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810833</v>
+        <v>122810808</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577054</v>
+        <v>576985</v>
       </c>
       <c r="R2" t="n">
-        <v>6433293</v>
+        <v>6433307</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810786</v>
+        <v>122810833</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,12 +822,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576947</v>
+        <v>577054</v>
       </c>
       <c r="R3" t="n">
-        <v>6433322</v>
+        <v>6433293</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810777</v>
+        <v>122810769</v>
       </c>
       <c r="B4" t="n">
-        <v>97301</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,39 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577111</v>
+        <v>577090</v>
       </c>
       <c r="R4" t="n">
-        <v>6433333</v>
+        <v>6433258</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +995,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810808</v>
+        <v>122810786</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,33 +1029,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576985</v>
+        <v>576947</v>
       </c>
       <c r="R5" t="n">
-        <v>6433307</v>
+        <v>6433322</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810769</v>
+        <v>122810777</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>97301</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,35 +1135,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577090</v>
+        <v>577111</v>
       </c>
       <c r="R6" t="n">
-        <v>6433258</v>
+        <v>6433333</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,6 +1219,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810808</v>
+        <v>122810777</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>97309</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576985</v>
+        <v>577111</v>
       </c>
       <c r="R2" t="n">
-        <v>6433307</v>
+        <v>6433333</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -771,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810833</v>
+        <v>122810769</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +802,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,16 +823,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577054</v>
+        <v>577090</v>
       </c>
       <c r="R3" t="n">
-        <v>6433293</v>
+        <v>6433258</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810769</v>
+        <v>122810786</v>
       </c>
       <c r="B4" t="n">
         <v>57494</v>
@@ -951,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577090</v>
+        <v>576947</v>
       </c>
       <c r="R4" t="n">
-        <v>6433258</v>
+        <v>6433322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810786</v>
+        <v>122810833</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,20 +1022,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,12 +1043,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576947</v>
+        <v>577054</v>
       </c>
       <c r="R5" t="n">
-        <v>6433322</v>
+        <v>6433293</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810777</v>
+        <v>122810808</v>
       </c>
       <c r="B6" t="n">
-        <v>97301</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,39 +1136,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577111</v>
+        <v>576985</v>
       </c>
       <c r="R6" t="n">
-        <v>6433333</v>
+        <v>6433307</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1219,7 +1220,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810769</v>
+        <v>122810833</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,12 +823,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -838,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577090</v>
+        <v>577054</v>
       </c>
       <c r="R3" t="n">
-        <v>6433258</v>
+        <v>6433293</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810786</v>
+        <v>122810769</v>
       </c>
       <c r="B4" t="n">
         <v>57494</v>
@@ -948,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576947</v>
+        <v>577090</v>
       </c>
       <c r="R4" t="n">
-        <v>6433322</v>
+        <v>6433258</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810833</v>
+        <v>122810786</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,20 +1026,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1043,16 +1047,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577054</v>
+        <v>576947</v>
       </c>
       <c r="R5" t="n">
-        <v>6433293</v>
+        <v>6433322</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810833</v>
+        <v>122810786</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,20 +802,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,16 +823,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577054</v>
+        <v>576947</v>
       </c>
       <c r="R3" t="n">
-        <v>6433293</v>
+        <v>6433322</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1014,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810786</v>
+        <v>122810833</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,20 +1022,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,12 +1043,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576947</v>
+        <v>577054</v>
       </c>
       <c r="R5" t="n">
-        <v>6433322</v>
+        <v>6433293</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810777</v>
+        <v>122810833</v>
       </c>
       <c r="B2" t="n">
-        <v>97309</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577111</v>
+        <v>577054</v>
       </c>
       <c r="R2" t="n">
-        <v>6433333</v>
+        <v>6433293</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810833</v>
+        <v>122810808</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1021,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,7 +1051,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577054</v>
+        <v>576985</v>
       </c>
       <c r="R5" t="n">
-        <v>6433293</v>
+        <v>6433307</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810808</v>
+        <v>122810777</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>97311</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,39 +1135,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576985</v>
+        <v>577111</v>
       </c>
       <c r="R6" t="n">
-        <v>6433307</v>
+        <v>6433333</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1220,6 +1219,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810833</v>
+        <v>122810808</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577054</v>
+        <v>576985</v>
       </c>
       <c r="R2" t="n">
-        <v>6433293</v>
+        <v>6433307</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810786</v>
+        <v>122810769</v>
       </c>
       <c r="B3" t="n">
         <v>57494</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576947</v>
+        <v>577090</v>
       </c>
       <c r="R3" t="n">
-        <v>6433322</v>
+        <v>6433258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810769</v>
+        <v>122810786</v>
       </c>
       <c r="B4" t="n">
         <v>57494</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577090</v>
+        <v>576947</v>
       </c>
       <c r="R4" t="n">
-        <v>6433258</v>
+        <v>6433322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810808</v>
+        <v>122810833</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,25 +1021,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1051,7 +1051,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576985</v>
+        <v>577054</v>
       </c>
       <c r="R5" t="n">
-        <v>6433307</v>
+        <v>6433293</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810808</v>
+        <v>122810786</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576985</v>
+        <v>576947</v>
       </c>
       <c r="R2" t="n">
-        <v>6433307</v>
+        <v>6433322</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810786</v>
+        <v>122810808</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,29 +911,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576947</v>
+        <v>576985</v>
       </c>
       <c r="R4" t="n">
-        <v>6433322</v>
+        <v>6433307</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810833</v>
+        <v>122810777</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>97319</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,35 +1025,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577054</v>
+        <v>577111</v>
       </c>
       <c r="R5" t="n">
-        <v>6433293</v>
+        <v>6433333</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,6 +1105,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810777</v>
+        <v>122810833</v>
       </c>
       <c r="B6" t="n">
-        <v>97311</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,35 +1140,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577111</v>
+        <v>577054</v>
       </c>
       <c r="R6" t="n">
-        <v>6433333</v>
+        <v>6433293</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,7 +1220,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810769</v>
+        <v>122810808</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,29 +801,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577090</v>
+        <v>576985</v>
       </c>
       <c r="R3" t="n">
-        <v>6433258</v>
+        <v>6433307</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810808</v>
+        <v>122810769</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,33 +915,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576985</v>
+        <v>577090</v>
       </c>
       <c r="R4" t="n">
-        <v>6433307</v>
+        <v>6433258</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810786</v>
+        <v>122810808</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576947</v>
+        <v>576985</v>
       </c>
       <c r="R2" t="n">
-        <v>6433322</v>
+        <v>6433307</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810808</v>
+        <v>122810777</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>97319</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,39 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576985</v>
+        <v>577111</v>
       </c>
       <c r="R3" t="n">
-        <v>6433307</v>
+        <v>6433333</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810769</v>
+        <v>122810786</v>
       </c>
       <c r="B4" t="n">
         <v>57494</v>
@@ -947,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577090</v>
+        <v>576947</v>
       </c>
       <c r="R4" t="n">
-        <v>6433258</v>
+        <v>6433322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810777</v>
+        <v>122810769</v>
       </c>
       <c r="B5" t="n">
-        <v>97319</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,39 +1026,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577111</v>
+        <v>577090</v>
       </c>
       <c r="R5" t="n">
-        <v>6433333</v>
+        <v>6433258</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1106,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810808</v>
+        <v>122810833</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576985</v>
+        <v>577054</v>
       </c>
       <c r="R2" t="n">
-        <v>6433307</v>
+        <v>6433293</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810777</v>
+        <v>122810769</v>
       </c>
       <c r="B3" t="n">
-        <v>97319</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577111</v>
+        <v>577090</v>
       </c>
       <c r="R3" t="n">
-        <v>6433333</v>
+        <v>6433258</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810786</v>
+        <v>122810808</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,29 +915,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -952,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576947</v>
+        <v>576985</v>
       </c>
       <c r="R4" t="n">
-        <v>6433322</v>
+        <v>6433307</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810769</v>
+        <v>122810777</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>97319</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,35 +1025,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577090</v>
+        <v>577111</v>
       </c>
       <c r="R5" t="n">
-        <v>6433258</v>
+        <v>6433333</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,6 +1109,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810833</v>
+        <v>122810786</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,20 +1140,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1157,16 +1161,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577054</v>
+        <v>576947</v>
       </c>
       <c r="R6" t="n">
-        <v>6433293</v>
+        <v>6433322</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810833</v>
+        <v>122810808</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577054</v>
+        <v>576985</v>
       </c>
       <c r="R2" t="n">
-        <v>6433293</v>
+        <v>6433307</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810769</v>
+        <v>122810786</v>
       </c>
       <c r="B3" t="n">
         <v>57494</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577090</v>
+        <v>576947</v>
       </c>
       <c r="R3" t="n">
-        <v>6433258</v>
+        <v>6433322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810808</v>
+        <v>122810833</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,7 +941,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576985</v>
+        <v>577054</v>
       </c>
       <c r="R4" t="n">
-        <v>6433307</v>
+        <v>6433293</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810777</v>
+        <v>122810769</v>
       </c>
       <c r="B5" t="n">
-        <v>97319</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,39 +1025,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577111</v>
+        <v>577090</v>
       </c>
       <c r="R5" t="n">
-        <v>6433333</v>
+        <v>6433258</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1105,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810786</v>
+        <v>122810777</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>97319</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,35 +1135,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576947</v>
+        <v>577111</v>
       </c>
       <c r="R6" t="n">
-        <v>6433322</v>
+        <v>6433333</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,6 +1219,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810808</v>
+        <v>122810777</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>97322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576985</v>
+        <v>577111</v>
       </c>
       <c r="R2" t="n">
-        <v>6433307</v>
+        <v>6433333</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -771,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810786</v>
+        <v>122810769</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576947</v>
+        <v>577090</v>
       </c>
       <c r="R3" t="n">
-        <v>6433322</v>
+        <v>6433258</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810833</v>
+        <v>122810786</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,20 +912,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,16 +933,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577054</v>
+        <v>576947</v>
       </c>
       <c r="R4" t="n">
-        <v>6433293</v>
+        <v>6433322</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810769</v>
+        <v>122810808</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,29 +1026,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577090</v>
+        <v>576985</v>
       </c>
       <c r="R5" t="n">
-        <v>6433258</v>
+        <v>6433307</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810777</v>
+        <v>122810833</v>
       </c>
       <c r="B6" t="n">
-        <v>97319</v>
+        <v>57851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,35 +1140,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577111</v>
+        <v>577054</v>
       </c>
       <c r="R6" t="n">
-        <v>6433333</v>
+        <v>6433293</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,7 +1220,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810777</v>
+        <v>122810769</v>
       </c>
       <c r="B2" t="n">
-        <v>97322</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577111</v>
+        <v>577090</v>
       </c>
       <c r="R2" t="n">
-        <v>6433333</v>
+        <v>6433258</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810769</v>
+        <v>122810777</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>97324</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +797,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577090</v>
+        <v>577111</v>
       </c>
       <c r="R3" t="n">
-        <v>6433258</v>
+        <v>6433333</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810786</v>
+        <v>122810833</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,20 +912,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -933,12 +933,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -948,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576947</v>
+        <v>577054</v>
       </c>
       <c r="R4" t="n">
-        <v>6433322</v>
+        <v>6433293</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1124,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810833</v>
+        <v>122810786</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,20 +1140,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1157,16 +1161,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577054</v>
+        <v>576947</v>
       </c>
       <c r="R6" t="n">
-        <v>6433293</v>
+        <v>6433322</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810769</v>
+        <v>122810777</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>97324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577090</v>
+        <v>577111</v>
       </c>
       <c r="R2" t="n">
-        <v>6433258</v>
+        <v>6433333</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810777</v>
+        <v>122810769</v>
       </c>
       <c r="B3" t="n">
-        <v>97324</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,39 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577111</v>
+        <v>577090</v>
       </c>
       <c r="R3" t="n">
-        <v>6433333</v>
+        <v>6433258</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810777</v>
+        <v>122810833</v>
       </c>
       <c r="B2" t="n">
-        <v>97324</v>
+        <v>57851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577111</v>
+        <v>577054</v>
       </c>
       <c r="R2" t="n">
-        <v>6433333</v>
+        <v>6433293</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810769</v>
+        <v>122810786</v>
       </c>
       <c r="B3" t="n">
         <v>57497</v>
@@ -838,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577090</v>
+        <v>576947</v>
       </c>
       <c r="R3" t="n">
-        <v>6433258</v>
+        <v>6433322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810833</v>
+        <v>122810777</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>97330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,35 +915,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577054</v>
+        <v>577111</v>
       </c>
       <c r="R4" t="n">
-        <v>6433293</v>
+        <v>6433333</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810786</v>
+        <v>122810769</v>
       </c>
       <c r="B6" t="n">
         <v>57497</v>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576947</v>
+        <v>577090</v>
       </c>
       <c r="R6" t="n">
-        <v>6433322</v>
+        <v>6433258</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810833</v>
+        <v>122810808</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577054</v>
+        <v>576985</v>
       </c>
       <c r="R2" t="n">
-        <v>6433293</v>
+        <v>6433307</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810786</v>
+        <v>122810777</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>97333</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576947</v>
+        <v>577111</v>
       </c>
       <c r="R3" t="n">
-        <v>6433322</v>
+        <v>6433333</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122810777</v>
+        <v>122810833</v>
       </c>
       <c r="B4" t="n">
-        <v>97330</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +920,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577111</v>
+        <v>577054</v>
       </c>
       <c r="R4" t="n">
-        <v>6433333</v>
+        <v>6433293</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +1000,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810808</v>
+        <v>122810769</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,33 +1034,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576985</v>
+        <v>577090</v>
       </c>
       <c r="R5" t="n">
-        <v>6433307</v>
+        <v>6433258</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810769</v>
+        <v>122810786</v>
       </c>
       <c r="B6" t="n">
         <v>57497</v>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577090</v>
+        <v>576947</v>
       </c>
       <c r="R6" t="n">
-        <v>6433258</v>
+        <v>6433322</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 6472-2025 artfynd.xlsx
+++ b/artfynd/A 6472-2025 artfynd.xlsx
@@ -675,49 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122810808</v>
+        <v>122810769</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576985</v>
+        <v>577090</v>
       </c>
       <c r="R2" t="n">
-        <v>6433307</v>
+        <v>6433258</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122810777</v>
+        <v>122810786</v>
       </c>
       <c r="B3" t="n">
-        <v>97333</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,35 +791,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +823,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577111</v>
+        <v>576947</v>
       </c>
       <c r="R3" t="n">
-        <v>6433333</v>
+        <v>6433322</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +867,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,12 +888,7 @@
         <v>122810833</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,15 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122810769</v>
+        <v>122810808</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,29 +1005,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577090</v>
+        <v>576985</v>
       </c>
       <c r="R5" t="n">
-        <v>6433258</v>
+        <v>6433307</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,47 +1103,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122810786</v>
+        <v>122810777</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576947</v>
+        <v>577111</v>
       </c>
       <c r="R6" t="n">
-        <v>6433322</v>
+        <v>6433333</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,6 +1194,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
